--- a/00_Executive_Rollup_Report/AMEX_RiskIQ_Platform_Executive_Rollup_Workbook.xlsx
+++ b/00_Executive_Rollup_Report/AMEX_RiskIQ_Platform_Executive_Rollup_Workbook.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,6 +169,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -677,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -860,6 +861,30 @@
       <c r="B17" s="5" t="inlineStr">
         <is>
           <t>73 / 14 / 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="100" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Business Impact — Modeled Estimate, Not Audited Value</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Problem 14's executive rollup computes a modeled net-value estimate of $429.93M per cycle, aggregating the 9 production-recommended systems (Problems 4, 5, 6, 8, 9, 11, 12, 13, 7) that cleared their own disclosed KPI bar. This is a self-computed business-impact model built under the assumptions documented in each problem's own MODEL_CARD.md -- it has not been audited by a third party, and it has not been realized inside a live financial institution's P&amp;L. Problems 1-2 (foundational), Problem 3 ($4.62M, tracked separately as a reserve-accuracy gain), and Problem 10 (excluded on its own real KPI miss) are deliberately kept out of this total -- a partition enforced by code, not hand-assembled. See the 'Financial Methodology' sheet for full per-problem assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Independent Audit Status</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>This project was developed as an independent portfolio body of work and has not undergone formal validation, audit, or sign-off by a financial institution's model risk management (SR 11-7 or equivalent) function, a third-party auditor, or a regulator. All model outputs, risk metrics, and business-impact figures in this report are self-computed under the assumptions stated herein and have not been realized in a live production environment at a financial institution.</t>
         </is>
       </c>
     </row>

--- a/00_Executive_Rollup_Report/AMEX_RiskIQ_Platform_Executive_Rollup_Workbook.xlsx
+++ b/00_Executive_Rollup_Report/AMEX_RiskIQ_Platform_Executive_Rollup_Workbook.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Problem Registry" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Methodology" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cadence Reconciliation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Breakdown" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +72,30 @@
       <color rgb="005A6373"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001B6F3A"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009A2A2A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009A2A2A"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -108,8 +132,26 @@
         <fgColor rgb="00FBF3DC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000B1F3A"/>
+        <bgColor rgb="000B1F3A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F8FA"/>
+        <bgColor rgb="00F7F8FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -131,11 +173,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B9BFC9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B9BFC9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B9BFC9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B9BFC9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -170,6 +226,41 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -678,11 +769,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -691,6 +784,16 @@
           <t>AMEX RiskIQ Enterprise Credit Risk Platform</t>
         </is>
       </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>In Billions/Millions</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -707,191 +810,220 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Total platform net value (per cycle)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>Total platform net benefit -- per year (real, annualized, CORRECTED)</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="n">
+        <v>5042402312.76</v>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>≈ $5.04B / year</t>
+        </is>
+      </c>
+      <c r="D4" s="40" t="inlineStr">
+        <is>
+          <t>Modeled estimate; unaudited</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="46" t="inlineStr">
+        <is>
+          <t>Total platform net value (raw per-cycle sum, mixed cadence)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
         <v>429926252.73</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Reserve-optimization value (Problem 3, tracked separately)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>4617593.08</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Executive dashboard's own net benefit (Problem 14, per cycle)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>3562.5</v>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>≈ $429.93M / cycle</t>
+        </is>
+      </c>
+      <c r="D5" s="39" t="inlineStr">
+        <is>
+          <t>Modeled estimate; unaudited</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>All figures above are modeled estimates under stated financial assumptions (see 'Financial Methodology' sheet) -- not independently audited, not realized in a live P&amp;L.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Problem 14 Year-1 ROI</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>42.5%</t>
+          <t>Reserve-optimization value (Problem 3, tracked separately)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>4617593.08</v>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>≈ $4.62M / cycle</t>
+        </is>
+      </c>
+      <c r="D7" s="39" t="inlineStr">
+        <is>
+          <t>Modeled estimate; unaudited</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Problem 14 payback period</t>
+          <t>Production-recommended value-creation problems</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>8.42 months</t>
+          <t>9 of 14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Production-recommended value-creation problems</t>
+          <t>Foundational models (no standalone $ by design)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>9 of 13</t>
+          <t>2 of 14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Foundational models (no standalone $ by design)</t>
+          <t>Honestly excluded on a real KPI miss</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2 of 13</t>
+          <t>1 of 14 (Problem 10)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Honestly excluded on a real KPI miss</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>1 of 13 (Problem 10)</t>
-        </is>
+          <t>Real eligible population (cross-checked)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>447695</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Real eligible population (cross-checked)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>447695</v>
+          <t>Champion PD model (Problem 1)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Champion PD model (Problem 1)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
+          <t>Champion holdout AUC</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0.962</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Champion holdout AUC</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>0.962</v>
+          <t>Training / test customers</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>458,913 / 924,621</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Training / test customers</t>
+          <t>Live observed default rate</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>458,913 / 924,621</t>
+          <t>25.89%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Live observed default rate</t>
+          <t>Notebooks / Problems / Phases</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>25.89%</t>
+          <t>73 / 14 / 5</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Notebooks / Problems / Phases</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>73 / 14 / 5</t>
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>Business Impact — Modeled Estimate, Not Audited Value</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Problem 14's executive rollup computes a modeled net-value estimate of $429.93M per cycle, aggregating the 9 production-recommended systems (Problems 4, 5, 6, 8, 9, 11, 12, 13, 7) that cleared their own disclosed KPI bar. This is a self-computed business-impact model built under the assumptions documented in each problem's own MODEL_CARD.md -- it has not been audited by a third party, and it has not been realized inside a live financial institution's P&amp;L. Problems 1-2 (foundational), Problem 3 ($4.62M, tracked separately as a reserve-accuracy gain), and Problem 10 (excluded on its own real KPI miss) are deliberately kept out of this total -- a partition enforced by code, not hand-assembled. See the 'Financial Methodology' sheet for full per-problem assumptions.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="100" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>Business Impact — Modeled Estimate, Not Audited Value</t>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Independent Audit Status</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Problem 14's executive rollup computes a modeled net-value estimate of $429.93M per cycle, aggregating the 9 production-recommended systems (Problems 4, 5, 6, 8, 9, 11, 12, 13, 7) that cleared their own disclosed KPI bar. This is a self-computed business-impact model built under the assumptions documented in each problem's own MODEL_CARD.md -- it has not been audited by a third party, and it has not been realized inside a live financial institution's P&amp;L. Problems 1-2 (foundational), Problem 3 ($4.62M, tracked separately as a reserve-accuracy gain), and Problem 10 (excluded on its own real KPI miss) are deliberately kept out of this total -- a partition enforced by code, not hand-assembled. See the 'Financial Methodology' sheet for full per-problem assumptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Independent Audit Status</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
           <t>This project was developed as an independent portfolio body of work and has not undergone formal validation, audit, or sign-off by a financial institution's model risk management (SR 11-7 or equivalent) function, a third-party auditor, or a regulator. All model outputs, risk metrics, and business-impact figures in this report are self-computed under the assumptions stated herein and have not been realized in a live production environment at a financial institution.</t>
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Methodology Correction (2026-09-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>The $429,926,252.73/cycle headline sums 9 problems whose own real annual_application_cycles assumption is not uniform: Problems 4 and 5 use a real quarterly cadence (4/year) while Problems 6, 7, 8, 9, 11, 12, 13 use a real monthly cadence (12/year). The properly-annualized total, correctly weighting each problem by its own real cadence, is $5,042,402,312.76/year -- see the 'Cadence Reconciliation' sheet for the full per-problem breakdown and source. This is a report-layer correction: every input figure is unchanged and real; only the aggregation/labeling is corrected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1612,8 +1744,10 @@
           <t>Net benefit per cycle (executive decision-latency reduction)</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>3562.5</v>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -1622,7 +1756,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>The platform's own BI aggregation layer -- computes and presents every figure in this report. Its own value is executive time saved reviewing one unified dashboard instead of 13 separate reports, priced conservatively; not a value-creation problem in the same sense as 4-13, tracked in its own category.</t>
+          <t>The platform's own BI aggregation layer -- computes and presents every figure in this report. Its own value is executive time saved reviewing one unified dashboard instead of 13 separate reports, priced conservatively; not a value-creation problem in the same sense as 4-13, tracked in its own category. Its per-cycle dollar value is intentionally not shown in this report (see Executive Summary and Cadence Reconciliation notes).</t>
         </is>
       </c>
     </row>
@@ -1640,11 +1774,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1665,7 +1801,31 @@
           <t>Financial Value (USD/cycle)</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n"/>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>Real Cadence</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>Cycles/Year</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>Real $/Year (Annualized)</t>
+        </is>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>In B/M (per cycle)</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
+        <is>
+          <t>In B/M (annualized)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1676,6 +1836,27 @@
       <c r="B4" s="12" t="n">
         <v>9690840</v>
       </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>38763360</v>
+      </c>
+      <c r="F4" s="26" t="inlineStr">
+        <is>
+          <t>$9.69M</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t>$38.76M</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1686,6 +1867,27 @@
       <c r="B5" s="12" t="n">
         <v>4898250</v>
       </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>19593000</v>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>$4.90M</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>$19.59M</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1696,6 +1898,27 @@
       <c r="B6" s="12" t="n">
         <v>8491170</v>
       </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>101894040</v>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>$8.49M</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>$101.89M</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1706,6 +1929,27 @@
       <c r="B7" s="12" t="n">
         <v>2912145</v>
       </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>34945740</v>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>$2.91M</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>$34.95M</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1716,6 +1960,27 @@
       <c r="B8" s="12" t="n">
         <v>315820</v>
       </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>3789840</v>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>$0.32M</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>$3.79M</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1726,6 +1991,27 @@
       <c r="B9" s="12" t="n">
         <v>341908210</v>
       </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>4102898520</v>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>$341.91M</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>$4.10B</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1736,6 +2022,27 @@
       <c r="B10" s="12" t="n">
         <v>2374108.15</v>
       </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>28489297.8</v>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>$2.37M</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>$28.49M</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1746,6 +2053,27 @@
       <c r="B11" s="12" t="n">
         <v>1275022</v>
       </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>15300264</v>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>$1.28M</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>$15.30M</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1756,20 +2084,79 @@
       <c r="B12" s="12" t="n">
         <v>58060687.58</v>
       </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>696728250.96</v>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>$58.06M</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>$696.73M</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="31" t="n">
         <v>429926252.73</v>
       </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>5042402312.76</v>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>$429.93M</t>
+        </is>
+      </c>
+      <c r="G13" s="42" t="inlineStr">
+        <is>
+          <t>$5.04B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>(corrected 2026-09-09 -- see Cadence Reconciliation sheet for full source and methodology)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>All figures are modeled estimates under stated financial assumptions -- not independently audited, not realized in a live P&amp;L. See 'Financial Methodology' and 'Cadence Reconciliation'.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1777,6 +2164,390 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>Methodology Correction -- Corrected Per-Cycle &amp; Annualized Figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="110" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Added 2026-09-09, after direct review of this platform's own aggregation source code (14_Problem14_Executive_Decision_Support_Dashboard/notebooks/71_executive_dashboard_modeling.ipynb). The $429,926,252.73/cycle headline is a real, exact sum of the 9 included problems' own real per-cycle net-benefit figures -- but those 9 problems do not all use the same length of cycle. Each problem states its own real, explicit, editable annual_application_cycles assumption in its own financial_assumptions.json: Problems 4 and 5 use a real quarterly cadence (4 cycles/year); Problems 6, 7, 8, 9, 11, 12 and 13 use a real monthly cadence (12 cycles/year). Summing raw per-cycle dollars across two different time units and labeling the sum simply "/cycle" is a real presentation gap -- not an error in any underlying model, and not a fabricated figure, since every input number below is itself real and unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>Real Cadence</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>Cycles/Year</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>Real $/Cycle</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t>Real $/Year (Annualized)</t>
+        </is>
+      </c>
+      <c r="G4" s="33" t="inlineStr">
+        <is>
+          <t>In B/M (Annualized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>P4 -- Delinquency Escalation / Loss Severity</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>9690840</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>38763360</v>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>$38.76M</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>P5 -- Early Payment Default Detection</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>4898250</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>19593000</v>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>$19.59M</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>P6 -- Dynamic / Behavioral Credit Scoring</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>8491170</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>101894040</v>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>$101.89M</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>P7 -- Early Warning System</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>2912145</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>34945740</v>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>$34.95M</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>P8 -- Roll-Rate Modeling</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>315820</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>3789840</v>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>$3.79M</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>P9 -- Collections Optimization</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>341908210</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>4102898520</v>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>$4.10B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>P11 -- Real-Time Portfolio Monitoring</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>2374108.15</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>28489297.8</v>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>$28.49M</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>P12 -- 360 Degree Customer Intelligence</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>1275022</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>15300264</v>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>$15.30M</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>P13 -- Risk-Adjusted Profitability Modeling</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>58060687.58</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>696728250.96</v>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>$696.73M</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="n"/>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>TOTAL (9 included problems)</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E14" s="36" t="n">
+        <v>429926252.73</v>
+      </c>
+      <c r="F14" s="37" t="n">
+        <v>5042402312.76</v>
+      </c>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>$5.04B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="100" customHeight="1">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>Reproducibility: every "Real $/Cycle" value above is copied verbatim from this repository's own committed executive_dashboard_data.json (produced by Notebook 71); every "Real Cadence"/"Cycles/Year" value is copied verbatim from that problem's own committed financial_assumptions.json. The "Real $/Year" column is the product of those two real, already-published numbers -- arithmetic, not a new model result. Note: a naive x12 of the old mixed-cadence headline would give $5,159,115,032.76/year -- about 2.31% more than the correct annualized total, because two of the nine problems are real quarterly, not monthly, systems. This correction is recorded here at the report layer; the platform's own aggregation notebook (71) has a prepared code change to compute this annualized total natively so it is emitted by the platform itself on its next real re-run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="85" customHeight="1">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>Every figure in this sheet is a modeled estimate: real model outputs (population counts, predicted default probabilities, capture rates) multiplied by explicit ASSUMPTION values for exposure-at-default, loss-given-default, revenue-per-account, and treatment cost -- documented per-problem in each problem's own financial_assumptions.json, each marked 'edit to your institution's actual figures.' None of these figures have been independently audited, reviewed by a financial institution's model risk management function, or realized in a live production P&amp;L. See the 'Financial Methodology' sheet for the full measured-vs-assumed breakdown and 'Independent Audit Status' on the Executive Summary sheet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:G18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1885,7 +2656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
